--- a/speech_statistics.xlsx
+++ b/speech_statistics.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,26 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>1 (n=41)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2 (n=52)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
@@ -446,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>115.87 [108.77; 122.96]</t>
+          <t>115.81 [108.71; 122.90]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>113.23 [106.28; 120.18]</t>
+          <t>113.20 [106.28; 120.13]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.8667</t>
         </is>
       </c>
     </row>
@@ -468,17 +480,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18.51 [16.02; 21.00]</t>
+          <t>18.18 [15.68; 20.68]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19.91 [17.58; 22.24]</t>
+          <t>19.90 [17.56; 22.23]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.5611</t>
         </is>
       </c>
     </row>
@@ -490,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>75.24 [74.10; 76.38]</t>
+          <t>75.18 [73.84; 76.52]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.14 [74.24; 76.05]</t>
+          <t>75.09 [73.89; 76.29]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.8847</t>
         </is>
       </c>
     </row>
@@ -512,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>273.74 [258.25; 289.23]</t>
+          <t>272.89 [257.21; 288.57]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>274.26 [261.29; 287.24]</t>
+          <t>273.69 [261.42; 285.95]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.5383</t>
         </is>
       </c>
     </row>
@@ -534,237 +546,2151 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>195.84 [180.04; 211.64]</t>
+          <t>194.92 [178.99; 210.86]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>199.08 [186.11; 212.05]</t>
+          <t>198.42 [186.21; 210.62]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.5332</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>median_pitch</t>
+          <t>hnr_mean</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.88 [105.55; 120.20]</t>
+          <t>9.57 [9.06; 10.09]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>109.31 [101.93; 116.70]</t>
+          <t>9.77 [9.28; 10.26]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.4304</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pitch_25_percentile</t>
+          <t>hnr_std</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>102.08 [95.88; 108.28]</t>
+          <t>4.46 [4.28; 4.64]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101.37 [94.94; 107.79]</t>
+          <t>4.56 [4.40; 4.72]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.7078</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pitch_75_percentile</t>
+          <t>voicing_ratio</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>123.21 [114.71; 131.70]</t>
+          <t>50.10 [47.22; 52.97]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>121.79 [113.35; 130.23]</t>
+          <t>53.44 [50.72; 56.16]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.0518</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hnr_mean</t>
+          <t>formant_f1_mean</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7.95 [7.36; 8.54]</t>
+          <t>650.77 [601.33; 700.21]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.70 [8.11; 9.29]</t>
+          <t>661.87 [618.27; 705.47]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.4083</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hnr_std</t>
+          <t>formant_f1_cv</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.11 [4.80; 5.43]</t>
+          <t>0.55 [0.51; 0.59]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.08 [4.84; 5.32]</t>
+          <t>0.56 [0.52; 0.60]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.5565</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hnr_min</t>
+          <t>formant_f2_mean</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-6.92 [-7.49; -6.35]</t>
+          <t>1911.04 [1844.28; 1977.80]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.82 [-7.30; -6.33]</t>
+          <t>1920.96 [1864.72; 1977.19]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.9343</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hnr_max</t>
+          <t>formant_f2_cv</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23.89 [21.89; 25.89]</t>
+          <t>0.20 [0.17; 0.23]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24.28 [22.70; 25.86]</t>
+          <t>0.21 [0.20; 0.23]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.6776</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>voicing_ratio</t>
+          <t>pause_count</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>50.10 [47.20; 52.99]</t>
+          <t>5.40 [3.40; 7.40]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>53.24 [50.51; 55.96]</t>
+          <t>5.14 [3.57; 6.70]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.9580</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mfcc_1</t>
+          <t>spectral_flux_mean</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-742.53 [-817.03; -668.03]</t>
+          <t>1.24 [1.18; 1.30]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-688.99 [-756.52; -621.46]</t>
+          <t>1.28 [1.24; 1.32]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.5169</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>spectral_flux_std</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.01 [0.90; 1.12]</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.99 [0.92; 1.06]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.2656</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>spectral_flux_cv</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.79 [0.75; 0.84]</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.77 [0.74; 0.81]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.2350</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>rms_cv</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.87 [0.83; 0.90]</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.83 [0.80; 0.86]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.1272</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>peaks_per_second</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4.96 [4.60; 5.31]</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5.00 [4.71; 5.30]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.4862</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>egemaps_00_F0semitoneFrom27.5Hz_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>23.96 [22.99; 24.92]</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>23.55 [22.59; 24.51]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.6957</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>egemaps_01_F0semitoneFrom27.5Hz_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.20 [0.19; 0.22]</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.19 [0.18; 0.20]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.0378</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>egemaps_02_F0semitoneFrom27.5Hz_sma3nz_percentile20.0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20.63 [19.61; 21.65]</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21.20 [20.18; 22.23]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.3250</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>egemaps_03_F0semitoneFrom27.5Hz_sma3nz_percentile50.0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>23.97 [22.85; 25.09]</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>23.64 [22.59; 24.69]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.8282</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>egemaps_04_F0semitoneFrom27.5Hz_sma3nz_percentile80.0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>26.06 [24.88; 27.23]</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>26.03 [24.94; 27.13]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.8442</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>egemaps_05_F0semitoneFrom27.5Hz_sma3nz_pctlrange0-2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4.89 [3.97; 5.82]</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4.64 [4.02; 5.26]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.3179</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>egemaps_06_F0semitoneFrom27.5Hz_sma3nz_meanRisingSlope</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>273.74 [238.47; 309.01]</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>220.66 [192.28; 249.03]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0.0579</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>egemaps_07_F0semitoneFrom27.5Hz_sma3nz_stddevRisingSlope</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>359.05 [298.81; 419.29]</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>324.95 [273.74; 376.15]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.2617</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>egemaps_08_F0semitoneFrom27.5Hz_sma3nz_meanFallingSlope</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>85.04 [72.22; 97.86]</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>77.52 [68.73; 86.30]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0.0441</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>egemaps_09_F0semitoneFrom27.5Hz_sma3nz_stddevFallingSlope</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>144.92 [101.99; 187.85]</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>104.73 [79.80; 129.67]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.0445</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>egemaps_10_loudness_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.76 [0.67; 0.84]</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.79 [0.72; 0.86]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0.3260</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>egemaps_11_loudness_sma3_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0.58 [0.55; 0.62]</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.55 [0.53; 0.58]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0.3106</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>egemaps_12_loudness_sma3_percentile20.0</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0.37 [0.32; 0.42]</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.39 [0.35; 0.44]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>egemaps_13_loudness_sma3_percentile50.0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0.67 [0.59; 0.75]</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.71 [0.64; 0.77]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.2818</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>egemaps_14_loudness_sma3_percentile80.0</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1.02 [0.90; 1.15]</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1.11 [1.01; 1.21]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.3854</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>egemaps_15_loudness_sma3_pctlrange0-2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0.64 [0.54; 0.74]</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0.70 [0.62; 0.78]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.6479</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>egemaps_16_loudness_sma3_meanRisingSlope</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>8.23 [7.24; 9.22]</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>8.35 [7.31; 9.40]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.6717</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>egemaps_17_loudness_sma3_stddevRisingSlope</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5.54 [4.82; 6.27]</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5.31 [4.66; 5.97]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.8602</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>egemaps_18_loudness_sma3_meanFallingSlope</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6.24 [5.32; 7.16]</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>6.68 [5.85; 7.52]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.6702</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>egemaps_19_loudness_sma3_stddevFallingSlope</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>4.57 [3.98; 5.16]</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4.80 [4.27; 5.34]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.9682</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>egemaps_20_spectralFlux_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0.45 [0.35; 0.55]</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.47 [0.41; 0.54]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0.6024</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>egemaps_21_spectralFlux_sma3_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0.84 [0.80; 0.89]</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.79 [0.75; 0.82]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0.1764</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>egemaps_22_mfcc1_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>18.58 [17.09; 20.06]</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>19.26 [18.09; 20.42]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0.5811</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>egemaps_23_mfcc1_sma3_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0.79 [0.68; 0.91]</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0.82 [0.70; 0.93]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0.8694</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>egemaps_24_mfcc2_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>13.67 [12.33; 15.00]</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>14.71 [13.48; 15.94]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0.0181</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>egemaps_25_mfcc2_sma3_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0.79 [-2.23; 3.81]</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0.72 [0.42; 1.02]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>0.3019</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>egemaps_26_mfcc3_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>13.03 [11.25; 14.80]</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>14.22 [12.56; 15.87]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>0.7442</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>egemaps_27_mfcc3_sma3_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0.92 [0.76; 1.08]</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.85 [0.09; 1.61]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.4326</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>egemaps_28_mfcc4_sma3_amean</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5.56 [3.69; 7.42]</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5.01 [3.74; 6.28]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.2416</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>egemaps_29_mfcc4_sma3_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.71 [-16.05; 19.47]</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1.74 [-5.12; 8.60]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.6991</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>egemaps_31_jitterLocal_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1.68 [1.58; 1.77]</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.74 [1.65; 1.83]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.4921</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>egemaps_32_shimmerLocaldB_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1.30 [1.25; 1.34]</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1.23 [1.20; 1.27]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.0885</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>egemaps_33_shimmerLocaldB_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0.72 [0.69; 0.74]</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.71 [0.69; 0.74]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.7487</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>egemaps_34_HNRdBACF_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2.87 [2.42; 3.32]</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.19 [2.71; 3.66]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.5754</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>egemaps_35_HNRdBACF_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.47 [0.29; 2.66]</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.23 [0.50; 1.97]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>0.4141</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>egemaps_36_logRelF0-H1-H2_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3.15 [2.04; 4.26]</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.41 [2.55; 4.27]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0.3440</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>egemaps_37_logRelF0-H1-H2_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3.83 [-28.53; 36.20]</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3.12 [-22.18; 28.42]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0.1468</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>egemaps_38_logRelF0-H1-A3_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>22.91 [21.86; 23.96]</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>24.96 [24.01; 25.92]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>0.0572</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>egemaps_39_logRelF0-H1-A3_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.54 [0.48; 0.60]</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0.49 [0.43; 0.54]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0.1214</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>egemaps_40_F1frequency_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>537.81 [520.77; 554.85]</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>531.13 [517.26; 544.99]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0.8542</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>egemaps_41_F1frequency_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0.43 [0.42; 0.45]</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0.44 [0.43; 0.45]</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>0.8632</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>egemaps_42_F1bandwidth_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1195.75 [1179.27; 1212.23]</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1203.86 [1191.72; 1216.00]</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.5323</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>egemaps_44_F1amplitudeLogRelF0_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-79.31 [-85.09; -73.53]</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-69.92 [-73.84; -65.99]</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.0587</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>egemaps_45_F1amplitudeLogRelF0_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>-1.09 [-1.15; -1.04]</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-1.20 [-1.25; -1.15]</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.0324</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>egemaps_46_F2frequency_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1592.54 [1569.74; 1615.35]</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1604.54 [1587.86; 1621.22]</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0.6324</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>egemaps_48_F2bandwidth_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>909.67 [885.23; 934.10]</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>918.93 [898.69; 939.17]</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.3603</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>egemaps_49_F2bandwidth_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0.39 [0.37; 0.41]</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0.40 [0.39; 0.42]</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>0.5170</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>egemaps_50_F2amplitudeLogRelF0_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-86.82 [-92.08; -81.56]</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>-79.94 [-83.51; -76.36]</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0.0831</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>egemaps_51_F2amplitudeLogRelF0_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>-0.92 [-0.96; -0.89]</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>-0.95 [-0.97; -0.92]</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>0.0862</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>egemaps_52_F3frequency_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2606.26 [2580.43; 2632.09]</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2647.03 [2626.25; 2667.81]</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0.0903</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>egemaps_54_F3bandwidth_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>818.34 [792.95; 843.73]</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>813.70 [792.60; 834.79]</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>0.8501</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>egemaps_55_F3bandwidth_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0.44 [0.42; 0.45]</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0.45 [0.43; 0.47]</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>0.0206</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>egemaps_56_F3amplitudeLogRelF0_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>-88.89 [-94.02; -83.77]</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>-82.71 [-86.14; -79.28]</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>0.1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>egemaps_57_F3amplitudeLogRelF0_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-0.89 [-0.92; -0.85]</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>-0.90 [-0.93; -0.88]</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0.1897</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>egemaps_58_alphaRatioV_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>-16.77 [-17.50; -16.05]</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>-17.82 [-18.55; -17.09]</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>0.1718</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>egemaps_59_alphaRatioV_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>-0.42 [-0.44; -0.40]</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>-0.40 [-0.42; -0.38]</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>0.0974</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>egemaps_60_hammarbergIndexV_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>25.09 [24.16; 26.01]</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>25.48 [24.70; 26.27]</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>0.0757</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>egemaps_61_hammarbergIndexV_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0.33 [0.31; 0.34]</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.32 [0.31; 0.34]</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0.0955</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>egemaps_63_slopeV0-500_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1.37 [-1.77; 4.51]</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1.12 [-36.91; 39.16]</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0.2286</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>egemaps_65_slopeV500-1500_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>-0.67 [-0.74; -0.60]</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>-0.64 [-0.68; -0.59]</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>0.1149</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>egemaps_66_spectralFluxV_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0.57 [0.45; 0.68]</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.59 [0.51; 0.67]</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0.8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>egemaps_67_spectralFluxV_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0.66 [0.61; 0.70]</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.66 [0.64; 0.69]</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0.6696</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>egemaps_68_mfcc1V_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>25.80 [24.52; 27.08]</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>25.94 [24.87; 27.01]</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0.8122</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>egemaps_69_mfcc1V_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0.43 [0.41; 0.45]</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.42 [0.40; 0.45]</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>0.9703</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>egemaps_70_mfcc2V_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>16.30 [14.81; 17.79]</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>17.50 [16.00; 19.00]</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>0.1115</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>egemaps_71_mfcc2V_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0.61 [0.40; 0.82]</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.53 [0.10; 0.97]</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0.9222</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>egemaps_72_mfcc3V_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>15.63 [13.91; 17.36]</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>16.85 [15.04; 18.67]</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>0.7938</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>egemaps_73_mfcc3V_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0.79 [0.69; 0.90]</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.74 [-0.13; 1.62]</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0.5032</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>egemaps_74_mfcc4V_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>6.30 [4.12; 8.48]</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5.29 [3.77; 6.81]</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0.1146</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>egemaps_75_mfcc4V_sma3nz_stddevNorm</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1.50 [-2.43; 5.43]</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1.52 [-1.29; 4.32]</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>0.6003</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>egemaps_76_alphaRatioUV_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>-3.55 [-4.49; -2.62]</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>-2.77 [-3.63; -1.92]</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0.8460</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>egemaps_77_hammarbergIndexUV_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10.08 [8.92; 11.25]</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>9.02 [7.98; 10.06]</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>0.8413</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>egemaps_80_spectralFluxUV_sma3nz_amean</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0.23 [0.18; 0.29]</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.27 [0.23; 0.30]</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>0.5241</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>egemaps_81_loudnessPeaksPerSec</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>3.01 [2.79; 3.24]</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3.15 [2.94; 3.37]</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0.4876</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>egemaps_82_VoicedSegmentsPerSec</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2.51 [2.39; 2.63]</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2.40 [2.29; 2.50]</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0.2272</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>egemaps_83_MeanVoicedSegmentLengthSec</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0.25 [0.24; 0.27]</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.27 [0.26; 0.29]</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0.0081</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>egemaps_84_StddevVoicedSegmentLengthSec</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0.24 [0.22; 0.26]</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.26 [0.24; 0.27]</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0.0821</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>egemaps_85_MeanUnvoicedSegmentLength</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0.14 [0.12; 0.16]</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.13 [0.11; 0.14]</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0.3519</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>egemaps_86_StddevUnvoicedSegmentLength</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0.15 [0.12; 0.17]</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.14 [0.11; 0.16]</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>0.5423</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>egemaps_87_equivalentSoundLevel_dBp</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>-26.55 [-27.77; -25.34]</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>-25.91 [-26.84; -24.98]</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0.4028</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>spectral_centroid</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>4030.10 [3507.25; 4552.95]</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>4280.43 [3925.10; 4635.75]</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>0.5183</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>spectral_rolloff</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>8287.42 [7313.74; 9261.10]</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>8868.28 [8166.52; 9570.05]</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>0.4079</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>zero_crossing_rate</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0.09 [0.07; 0.11]</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.10 [0.09; 0.10]</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>0.8618</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>total_duration</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>66.56 [58.61; 74.50]</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>65.73 [60.86; 70.61]</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>66.56 [58.65; 74.46]</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>65.24 [60.47; 70.01]</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0.2044</t>
         </is>
       </c>
     </row>

--- a/speech_statistics.xlsx
+++ b/speech_statistics.xlsx
@@ -436,12 +436,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>1 (n=41)</t>
+          <t>1 (n=95)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2 (n=52)</t>
+          <t>2 (n=56)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>115.81 [108.71; 122.90]</t>
+          <t>117.51 [112.28; 122.74]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>113.20 [106.28; 120.13]</t>
+          <t>113.20 [106.56; 119.85]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.8667</t>
+          <t>0.5334</t>
         </is>
       </c>
     </row>
@@ -480,17 +480,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18.18 [15.68; 20.68]</t>
+          <t>18.34 [16.70; 19.99]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19.90 [17.56; 22.23]</t>
+          <t>19.94 [17.61; 22.28]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.5611</t>
+          <t>0.1303</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>75.18 [73.84; 76.52]</t>
+          <t>75.27 [73.91; 76.64]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.09 [73.89; 76.29]</t>
+          <t>75.04 [73.91; 76.16]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.8847</t>
+          <t>0.0311</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>272.89 [257.21; 288.57]</t>
+          <t>262.99 [251.50; 274.48]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>273.69 [261.42; 285.95]</t>
+          <t>281.12 [269.44; 292.80]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5383</t>
+          <t>0.0194</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>194.92 [178.99; 210.86]</t>
+          <t>186.96 [175.21; 198.71]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>198.42 [186.21; 210.62]</t>
+          <t>199.09 [187.43; 210.76]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.5332</t>
+          <t>0.0111</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9.57 [9.06; 10.09]</t>
+          <t>10.20 [9.73; 10.67]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.77 [9.28; 10.26]</t>
+          <t>9.56 [9.07; 10.05]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.4304</t>
+          <t>0.0582</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.46 [4.28; 4.64]</t>
+          <t>4.58 [4.44; 4.71]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.56 [4.40; 4.72]</t>
+          <t>4.53 [4.38; 4.68]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.7078</t>
+          <t>0.4411</t>
         </is>
       </c>
     </row>
@@ -612,17 +612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>50.10 [47.22; 52.97]</t>
+          <t>49.84 [47.54; 52.14]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>53.44 [50.72; 56.16]</t>
+          <t>53.51 [50.86; 56.16]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.0518</t>
+          <t>0.0039</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>650.77 [601.33; 700.21]</t>
+          <t>684.90 [647.31; 722.48]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>661.87 [618.27; 705.47]</t>
+          <t>660.80 [618.84; 702.77]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.4083</t>
+          <t>0.0875</t>
         </is>
       </c>
     </row>
@@ -656,17 +656,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.55 [0.51; 0.59]</t>
+          <t>0.52 [0.50; 0.55]</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.56 [0.52; 0.60]</t>
+          <t>0.56 [0.51; 0.61]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.5565</t>
+          <t>0.1661</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1911.04 [1844.28; 1977.80]</t>
+          <t>1961.63 [1920.36; 2002.91]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1920.96 [1864.72; 1977.19]</t>
+          <t>1912.81 [1859.48; 1966.14]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.9343</t>
+          <t>0.0505</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.20 [0.17; 0.23]</t>
+          <t>0.20 [0.19; 0.22]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -710,139 +710,139 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.6776</t>
+          <t>0.7865</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pause_count</t>
+          <t>formant_f3_mean</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5.40 [3.40; 7.40]</t>
+          <t>2969.90 [2927.33; 3012.48]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5.14 [3.57; 6.70]</t>
+          <t>2954.19 [2907.72; 3000.67]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.9580</t>
+          <t>0.9428</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>spectral_flux_mean</t>
+          <t>formant_f3_cv</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.24 [1.18; 1.30]</t>
+          <t>0.13 [0.12; 0.14]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.28 [1.24; 1.32]</t>
+          <t>0.12 [0.11; 0.13]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.5169</t>
+          <t>0.1137</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>spectral_flux_std</t>
+          <t>lgdv_pause_percent</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.01 [0.90; 1.12]</t>
+          <t>0.16 [0.14; 0.18]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.99 [0.92; 1.06]</t>
+          <t>0.18 [0.16; 0.20]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.2656</t>
+          <t>0.0009</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>spectral_flux_cv</t>
+          <t>lgdv_pause_rate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.79 [0.75; 0.84]</t>
+          <t>2.21 [0.99; 3.43]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.77 [0.74; 0.81]</t>
+          <t>4.70 [3.22; 6.18]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.2350</t>
+          <t>0.1378</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>rms_cv</t>
+          <t>lgdv_loudness_cv</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.87 [0.83; 0.90]</t>
+          <t>0.85 [0.82; 0.88]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.83 [0.80; 0.86]</t>
+          <t>0.82 [0.79; 0.85]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.1272</t>
+          <t>0.1522</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>peaks_per_second</t>
+          <t>lgdv_spectral_flux_cv</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.96 [4.60; 5.31]</t>
+          <t>0.73 [0.70; 0.76]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5.00 [4.71; 5.30]</t>
+          <t>0.80 [0.76; 0.83]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.4862</t>
+          <t>0.1166</t>
         </is>
       </c>
     </row>
@@ -854,17 +854,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>23.96 [22.99; 24.92]</t>
+          <t>23.56 [22.90; 24.22]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23.55 [22.59; 24.51]</t>
+          <t>23.63 [22.72; 24.54]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.6957</t>
+          <t>0.9165</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.20 [0.19; 0.22]</t>
+          <t>0.20 [0.18; 0.21]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.0378</t>
+          <t>0.1037</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20.63 [19.61; 21.65]</t>
+          <t>20.63 [19.83; 21.44]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>21.20 [20.18; 22.23]</t>
+          <t>21.20 [20.24; 22.17]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.3250</t>
+          <t>0.4830</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23.97 [22.85; 25.09]</t>
+          <t>23.97 [23.20; 24.74]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>23.64 [22.59; 24.69]</t>
+          <t>23.74 [22.74; 24.74]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.8282</t>
+          <t>0.7755</t>
         </is>
       </c>
     </row>
@@ -942,17 +942,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>26.06 [24.88; 27.23]</t>
+          <t>26.12 [25.32; 26.92]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26.03 [24.94; 27.13]</t>
+          <t>26.11 [25.06; 27.15]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.8442</t>
+          <t>0.8466</t>
         </is>
       </c>
     </row>
@@ -964,17 +964,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.89 [3.97; 5.82]</t>
+          <t>4.78 [4.07; 5.49]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4.64 [4.02; 5.26]</t>
+          <t>4.65 [4.06; 5.24]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.3179</t>
+          <t>0.2208</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>273.74 [238.47; 309.01]</t>
+          <t>257.15 [232.04; 282.26]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>220.66 [192.28; 249.03]</t>
+          <t>220.37 [193.89; 246.85]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.0579</t>
+          <t>0.1370</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>359.05 [298.81; 419.29]</t>
+          <t>318.62 [276.06; 361.17]</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>324.95 [273.74; 376.15]</t>
+          <t>313.76 [265.99; 361.53]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.2617</t>
+          <t>0.6127</t>
         </is>
       </c>
     </row>
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>85.04 [72.22; 97.86]</t>
+          <t>72.55 [61.66; 83.45]</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>77.52 [68.73; 86.30]</t>
+          <t>79.56 [68.91; 90.20]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.0441</t>
+          <t>0.7056</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>144.92 [101.99; 187.85]</t>
+          <t>103.92 [75.35; 132.49]</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>104.73 [79.80; 129.67]</t>
+          <t>108.39 [79.45; 137.33]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.0445</t>
+          <t>0.7240</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0.76 [0.67; 0.84]</t>
+          <t>0.75 [0.70; 0.79]</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.79 [0.72; 0.86]</t>
+          <t>0.77 [0.70; 0.83]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.3260</t>
+          <t>0.4691</t>
         </is>
       </c>
     </row>
@@ -1096,17 +1096,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0.58 [0.55; 0.62]</t>
+          <t>0.58 [0.55; 0.60]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.55 [0.53; 0.58]</t>
+          <t>0.57 [0.54; 0.60]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.3106</t>
+          <t>0.6910</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0.37 [0.32; 0.42]</t>
+          <t>0.37 [0.34; 0.40]</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.39 [0.35; 0.44]</t>
+          <t>0.37 [0.33; 0.41]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.1994</t>
+          <t>0.5038</t>
         </is>
       </c>
     </row>
@@ -1140,17 +1140,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0.67 [0.59; 0.75]</t>
+          <t>0.66 [0.62; 0.70]</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.71 [0.64; 0.77]</t>
+          <t>0.69 [0.62; 0.75]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.2818</t>
+          <t>0.3013</t>
         </is>
       </c>
     </row>
@@ -1162,17 +1162,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.02 [0.90; 1.15]</t>
+          <t>1.01 [0.94; 1.08]</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.11 [1.01; 1.21]</t>
+          <t>1.08 [0.98; 1.18]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.3854</t>
+          <t>0.4302</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0.64 [0.54; 0.74]</t>
+          <t>0.64 [0.58; 0.70]</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.70 [0.62; 0.78]</t>
+          <t>0.68 [0.61; 0.75]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.6479</t>
+          <t>0.4960</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8.23 [7.24; 9.22]</t>
+          <t>7.84 [7.20; 8.48]</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8.35 [7.31; 9.40]</t>
+          <t>8.13 [7.15; 9.10]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.6717</t>
+          <t>0.4001</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5.54 [4.82; 6.27]</t>
+          <t>5.22 [4.70; 5.74]</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5.31 [4.66; 5.97]</t>
+          <t>5.22 [4.60; 5.84]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.8602</t>
+          <t>0.9624</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6.24 [5.32; 7.16]</t>
+          <t>6.06 [5.50; 6.62]</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>6.68 [5.85; 7.52]</t>
+          <t>6.60 [5.82; 7.39]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.6702</t>
+          <t>0.3234</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1272,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4.57 [3.98; 5.16]</t>
+          <t>4.38 [4.01; 4.74]</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.80 [4.27; 5.34]</t>
+          <t>4.77 [4.27; 5.27]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.9682</t>
+          <t>0.3984</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0.45 [0.35; 0.55]</t>
+          <t>0.43 [0.38; 0.48]</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.47 [0.41; 0.54]</t>
+          <t>0.47 [0.41; 0.53]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.6024</t>
+          <t>0.2142</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0.84 [0.80; 0.89]</t>
+          <t>0.83 [0.80; 0.86]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.1764</t>
+          <t>0.3193</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18.58 [17.09; 20.06]</t>
+          <t>16.87 [15.77; 17.98]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>19.26 [18.09; 20.42]</t>
+          <t>19.30 [18.12; 20.48]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.5811</t>
+          <t>0.0002</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0.79 [0.68; 0.91]</t>
+          <t>0.84 [0.63; 1.05]</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.82 [0.70; 0.93]</t>
+          <t>0.81 [0.71; 0.92]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.8694</t>
+          <t>0.5913</t>
         </is>
       </c>
     </row>
@@ -1382,17 +1382,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13.67 [12.33; 15.00]</t>
+          <t>14.36 [13.38; 15.34]</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>14.71 [13.48; 15.94]</t>
+          <t>13.94 [12.73; 15.15]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.0181</t>
+          <t>0.9489</t>
         </is>
       </c>
     </row>
@@ -1404,17 +1404,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0.79 [-2.23; 3.81]</t>
+          <t>0.70 [-0.62; 2.02]</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.72 [0.42; 1.02]</t>
+          <t>0.74 [0.45; 1.02]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.3019</t>
+          <t>0.5702</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13.03 [11.25; 14.80]</t>
+          <t>12.42 [11.40; 13.44]</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>14.22 [12.56; 15.87]</t>
+          <t>14.37 [12.76; 15.98]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.7442</t>
+          <t>0.0191</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0.92 [0.76; 1.08]</t>
+          <t>1.00 [0.84; 1.16]</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>0.85 [0.09; 1.61]</t>
+          <t>0.85 [0.15; 1.56]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>0.4326</t>
+          <t>0.3026</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5.56 [3.69; 7.42]</t>
+          <t>6.47 [5.28; 7.67]</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5.01 [3.74; 6.28]</t>
+          <t>4.87 [3.51; 6.22]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>0.2416</t>
+          <t>0.0023</t>
         </is>
       </c>
     </row>
@@ -1492,17 +1492,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.71 [-16.05; 19.47]</t>
+          <t>1.31 [-6.28; 8.90]</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1.74 [-5.12; 8.60]</t>
+          <t>1.71 [-4.65; 8.06]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.6991</t>
+          <t>0.8809</t>
         </is>
       </c>
     </row>
@@ -1514,17 +1514,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.68 [1.58; 1.77]</t>
+          <t>1.65 [1.57; 1.73]</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1.74 [1.65; 1.83]</t>
+          <t>1.72 [1.64; 1.81]</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.4921</t>
+          <t>0.6130</t>
         </is>
       </c>
     </row>
@@ -1536,17 +1536,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.30 [1.25; 1.34]</t>
+          <t>1.23 [1.19; 1.27]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.23 [1.20; 1.27]</t>
+          <t>1.24 [1.20; 1.28]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.0885</t>
+          <t>0.1953</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0.72 [0.69; 0.74]</t>
+          <t>0.71 [0.69; 0.72]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.7487</t>
+          <t>0.9270</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.87 [2.42; 3.32]</t>
+          <t>2.80 [2.43; 3.18]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.19 [2.71; 3.66]</t>
+          <t>3.15 [2.71; 3.59]</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>0.5754</t>
+          <t>0.4800</t>
         </is>
       </c>
     </row>
@@ -1602,17 +1602,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.47 [0.29; 2.66]</t>
+          <t>1.37 [0.72; 2.03]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.23 [0.50; 1.97]</t>
+          <t>1.28 [0.60; 1.96]</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0.4141</t>
+          <t>0.7261</t>
         </is>
       </c>
     </row>
@@ -1624,17 +1624,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3.15 [2.04; 4.26]</t>
+          <t>3.31 [2.60; 4.02]</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.41 [2.55; 4.27]</t>
+          <t>3.42 [2.58; 4.27]</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.3440</t>
+          <t>0.3517</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1646,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3.83 [-28.53; 36.20]</t>
+          <t>3.27 [-35.05; 41.60]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.12 [-22.18; 28.42]</t>
+          <t>3.07 [-20.38; 26.51]</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1043</t>
         </is>
       </c>
     </row>
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22.91 [21.86; 23.96]</t>
+          <t>22.78 [21.90; 23.66]</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>24.96 [24.01; 25.92]</t>
+          <t>24.94 [24.01; 25.87]</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.0572</t>
+          <t>0.0020</t>
         </is>
       </c>
     </row>
@@ -1690,17 +1690,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0.54 [0.48; 0.60]</t>
+          <t>0.57 [0.48; 0.66]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0.49 [0.43; 0.54]</t>
+          <t>0.49 [0.44; 0.54]</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>0.1214</t>
+          <t>0.0024</t>
         </is>
       </c>
     </row>
@@ -1712,17 +1712,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>537.81 [520.77; 554.85]</t>
+          <t>550.70 [538.57; 562.83]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>531.13 [517.26; 544.99]</t>
+          <t>530.09 [516.93; 543.24]</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0.8542</t>
+          <t>0.0517</t>
         </is>
       </c>
     </row>
@@ -1734,17 +1734,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0.43 [0.42; 0.45]</t>
+          <t>0.44 [0.43; 0.44]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.44 [0.43; 0.45]</t>
+          <t>0.44 [0.42; 0.45]</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>0.8632</t>
+          <t>0.4316</t>
         </is>
       </c>
     </row>
@@ -1756,17 +1756,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1195.75 [1179.27; 1212.23]</t>
+          <t>1198.39 [1187.69; 1209.08]</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1203.86 [1191.72; 1216.00]</t>
+          <t>1205.68 [1193.86; 1217.50]</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>0.5323</t>
+          <t>0.0844</t>
         </is>
       </c>
     </row>
@@ -1778,17 +1778,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>-79.31 [-85.09; -73.53]</t>
+          <t>-82.03 [-86.86; -77.20]</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-69.92 [-73.84; -65.99]</t>
+          <t>-68.93 [-72.83; -65.03]</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>0.0587</t>
+          <t>0.0005</t>
         </is>
       </c>
     </row>
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>-1.09 [-1.15; -1.04]</t>
+          <t>-1.07 [-1.12; -1.03]</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-1.20 [-1.25; -1.15]</t>
+          <t>-1.21 [-1.25; -1.16]</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0.0324</t>
+          <t>0.0002</t>
         </is>
       </c>
     </row>
@@ -1822,17 +1822,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1592.54 [1569.74; 1615.35]</t>
+          <t>1619.96 [1603.80; 1636.12]</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1604.54 [1587.86; 1621.22]</t>
+          <t>1596.12 [1580.31; 1611.92]</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>0.6324</t>
+          <t>0.0573</t>
         </is>
       </c>
     </row>
@@ -1844,17 +1844,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>909.67 [885.23; 934.10]</t>
+          <t>904.03 [886.50; 921.55]</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>918.93 [898.69; 939.17]</t>
+          <t>918.93 [899.80; 938.07]</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.0330</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0.39 [0.37; 0.41]</t>
+          <t>0.40 [0.39; 0.42]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0.5170</t>
+          <t>0.3615</t>
         </is>
       </c>
     </row>
@@ -1888,17 +1888,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>-86.82 [-92.08; -81.56]</t>
+          <t>-89.37 [-93.74; -85.00]</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-79.94 [-83.51; -76.36]</t>
+          <t>-79.11 [-82.65; -75.57]</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.0831</t>
+          <t>0.0011</t>
         </is>
       </c>
     </row>
@@ -1910,17 +1910,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>-0.92 [-0.96; -0.89]</t>
+          <t>-0.91 [-0.93; -0.88]</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-0.95 [-0.97; -0.92]</t>
+          <t>-0.95 [-0.98; -0.92]</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>0.0862</t>
+          <t>0.0006</t>
         </is>
       </c>
     </row>
@@ -1932,17 +1932,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2606.26 [2580.43; 2632.09]</t>
+          <t>2653.26 [2634.38; 2672.14]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2647.03 [2626.25; 2667.81]</t>
+          <t>2642.74 [2621.57; 2663.90]</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.0903</t>
+          <t>0.2228</t>
         </is>
       </c>
     </row>
@@ -1954,17 +1954,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>818.34 [792.95; 843.73]</t>
+          <t>815.94 [797.93; 833.96]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>813.70 [792.60; 834.79]</t>
+          <t>818.70 [799.06; 838.35]</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>0.8501</t>
+          <t>0.1026</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0.44 [0.42; 0.45]</t>
+          <t>0.44 [0.42; 0.46]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>0.0206</t>
+          <t>0.6743</t>
         </is>
       </c>
     </row>
@@ -1998,17 +1998,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>-88.89 [-94.02; -83.77]</t>
+          <t>-91.32 [-95.55; -87.09]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>-82.71 [-86.14; -79.28]</t>
+          <t>-81.66 [-85.05; -78.27]</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.1073</t>
+          <t>0.0013</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>-0.89 [-0.92; -0.85]</t>
+          <t>-0.86 [-0.89; -0.84]</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.1897</t>
+          <t>0.0010</t>
         </is>
       </c>
     </row>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>-16.77 [-17.50; -16.05]</t>
+          <t>-16.78 [-17.28; -16.28]</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-17.82 [-18.55; -17.09]</t>
+          <t>-17.58 [-18.27; -16.89]</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.1718</t>
+          <t>0.0423</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>-0.42 [-0.44; -0.40]</t>
+          <t>-0.41 [-0.44; -0.38]</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1604</t>
         </is>
       </c>
     </row>
@@ -2086,17 +2086,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>25.09 [24.16; 26.01]</t>
+          <t>24.99 [24.32; 25.66]</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>25.48 [24.70; 26.27]</t>
+          <t>25.36 [24.59; 26.12]</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.0757</t>
+          <t>0.0567</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0.33 [0.31; 0.34]</t>
+          <t>0.32 [0.31; 0.34]</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>0.0955</t>
+          <t>0.2382</t>
         </is>
       </c>
     </row>
@@ -2130,17 +2130,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.37 [-1.77; 4.51]</t>
+          <t>1.00 [-44.12; 46.13]</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1.12 [-36.91; 39.16]</t>
+          <t>1.00 [-34.26; 36.25]</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.2286</t>
+          <t>0.1666</t>
         </is>
       </c>
     </row>
@@ -2152,17 +2152,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>-0.67 [-0.74; -0.60]</t>
+          <t>-0.67 [-0.72; -0.62]</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>-0.64 [-0.68; -0.59]</t>
+          <t>-0.63 [-0.67; -0.59]</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.0128</t>
         </is>
       </c>
     </row>
@@ -2174,17 +2174,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0.57 [0.45; 0.68]</t>
+          <t>0.53 [0.47; 0.59]</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.59 [0.51; 0.67]</t>
+          <t>0.58 [0.50; 0.66]</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.8310</t>
+          <t>0.5842</t>
         </is>
       </c>
     </row>
@@ -2196,17 +2196,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0.66 [0.61; 0.70]</t>
+          <t>0.66 [0.63; 0.69]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.66 [0.64; 0.69]</t>
+          <t>0.67 [0.64; 0.69]</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>0.6696</t>
+          <t>0.6942</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>25.80 [24.52; 27.08]</t>
+          <t>23.92 [23.01; 24.84]</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>25.94 [24.87; 27.01]</t>
+          <t>26.17 [25.13; 27.22]</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>0.8122</t>
+          <t>0.0004</t>
         </is>
       </c>
     </row>
@@ -2240,17 +2240,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0.43 [0.41; 0.45]</t>
+          <t>0.44 [0.41; 0.46]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0.42 [0.40; 0.45]</t>
+          <t>0.42 [0.40; 0.44]</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>0.9703</t>
+          <t>0.0919</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2262,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16.30 [14.81; 17.79]</t>
+          <t>17.68 [16.57; 18.78]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>17.50 [16.00; 19.00]</t>
+          <t>17.17 [15.67; 18.67]</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.1115</t>
+          <t>0.4967</t>
         </is>
       </c>
     </row>
@@ -2284,17 +2284,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0.61 [0.40; 0.82]</t>
+          <t>0.52 [0.39; 0.66]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0.53 [0.10; 0.97]</t>
+          <t>0.54 [0.14; 0.95]</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.9222</t>
+          <t>0.2820</t>
         </is>
       </c>
     </row>
@@ -2306,17 +2306,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15.63 [13.91; 17.36]</t>
+          <t>14.74 [13.68; 15.79]</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>16.85 [15.04; 18.67]</t>
+          <t>17.14 [15.40; 18.88]</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0.7938</t>
+          <t>0.1155</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2328,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0.79 [0.69; 0.90]</t>
+          <t>0.88 [0.60; 1.15]</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0.74 [-0.13; 1.62]</t>
+          <t>0.75 [-0.07; 1.56]</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>0.5032</t>
+          <t>0.5658</t>
         </is>
       </c>
     </row>
@@ -2350,17 +2350,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>6.30 [4.12; 8.48]</t>
+          <t>8.51 [7.08; 9.94]</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>5.29 [3.77; 6.81]</t>
+          <t>4.87 [3.30; 6.44]</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>0.1146</t>
+          <t>0.0018</t>
         </is>
       </c>
     </row>
@@ -2372,17 +2372,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.50 [-2.43; 5.43]</t>
+          <t>1.12 [-1.35; 3.59]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1.52 [-1.29; 4.32]</t>
+          <t>1.46 [-1.17; 4.08]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>0.6003</t>
+          <t>0.3537</t>
         </is>
       </c>
     </row>
@@ -2394,17 +2394,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>-3.55 [-4.49; -2.62]</t>
+          <t>-3.20 [-3.77; -2.64]</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>-2.77 [-3.63; -1.92]</t>
+          <t>-3.12 [-4.00; -2.24]</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>0.8460</t>
+          <t>0.6569</t>
         </is>
       </c>
     </row>
@@ -2416,17 +2416,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>10.08 [8.92; 11.25]</t>
+          <t>9.88 [9.15; 10.62]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>9.02 [7.98; 10.06]</t>
+          <t>9.07 [8.05; 10.09]</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>0.8413</t>
+          <t>0.7939</t>
         </is>
       </c>
     </row>
@@ -2438,17 +2438,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0.23 [0.18; 0.29]</t>
+          <t>0.24 [0.21; 0.27]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>0.27 [0.23; 0.30]</t>
+          <t>0.26 [0.22; 0.29]</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>0.5241</t>
+          <t>0.3528</t>
         </is>
       </c>
     </row>
@@ -2460,17 +2460,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>3.01 [2.79; 3.24]</t>
+          <t>2.96 [2.80; 3.12]</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3.15 [2.94; 3.37]</t>
+          <t>3.11 [2.92; 3.31]</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>0.4876</t>
+          <t>0.0553</t>
         </is>
       </c>
     </row>
@@ -2482,17 +2482,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2.51 [2.39; 2.63]</t>
+          <t>2.48 [2.38; 2.58]</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2.40 [2.29; 2.50]</t>
+          <t>2.49 [2.38; 2.60]</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0.2272</t>
+          <t>0.8126</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>0.27 [0.26; 0.29]</t>
+          <t>0.27 [0.25; 0.28]</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>0.0081</t>
+          <t>0.0103</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0.24 [0.22; 0.26]</t>
+          <t>0.23 [0.22; 0.25]</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>0.0821</t>
+          <t>0.0180</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>0.13 [0.11; 0.14]</t>
+          <t>0.12 [0.11; 0.14]</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>0.3519</t>
+          <t>0.0178</t>
         </is>
       </c>
     </row>
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0.15 [0.12; 0.17]</t>
+          <t>0.15 [0.13; 0.17]</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>0.14 [0.11; 0.16]</t>
+          <t>0.13 [0.11; 0.15]</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>0.5423</t>
+          <t>0.1454</t>
         </is>
       </c>
     </row>
@@ -2592,17 +2592,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>-26.55 [-27.77; -25.34]</t>
+          <t>-26.75 [-27.52; -25.98]</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>-25.91 [-26.84; -24.98]</t>
+          <t>-25.80 [-26.67; -24.92]</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>0.4028</t>
+          <t>0.0395</t>
         </is>
       </c>
     </row>
@@ -2614,17 +2614,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>4030.10 [3507.25; 4552.95]</t>
+          <t>4961.66 [4577.94; 5345.38]</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>4280.43 [3925.10; 4635.75]</t>
+          <t>4166.97 [3798.53; 4535.42]</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>0.5183</t>
+          <t>0.0000</t>
         </is>
       </c>
     </row>
@@ -2636,17 +2636,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8287.42 [7313.74; 9261.10]</t>
+          <t>10793.21 [10104.51; 11481.92]</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>8868.28 [8166.52; 9570.05]</t>
+          <t>8674.36 [7940.85; 9407.87]</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>0.4079</t>
+          <t>0.0000</t>
         </is>
       </c>
     </row>
@@ -2658,17 +2658,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0.09 [0.07; 0.11]</t>
+          <t>0.11 [0.09; 0.12]</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0.10 [0.09; 0.10]</t>
+          <t>0.09 [0.09; 0.10]</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>0.8618</t>
+          <t>0.0001</t>
         </is>
       </c>
     </row>
@@ -2680,17 +2680,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>66.56 [58.65; 74.46]</t>
+          <t>59.21 [53.38; 65.04]</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>65.24 [60.47; 70.01]</t>
+          <t>65.86 [61.28; 70.43]</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>0.2044</t>
+          <t>0.0134</t>
         </is>
       </c>
     </row>
